--- a/data/coefficients.xlsx
+++ b/data/coefficients.xlsx
@@ -434,7 +434,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="24.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="8.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
